--- a/XII B INFORMATION.xlsx
+++ b/XII B INFORMATION.xlsx
@@ -4068,7 +4068,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG84"/>
+  <dimension ref="A1:AG69"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.1796875" customWidth="1"/>
@@ -9706,17 +9706,17 @@
       <c r="AC64" s="56"/>
       <c r="AF64" s="119"/>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="65" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AA65" s="78"/>
       <c r="AB65" s="78"/>
       <c r="AC65" s="79"/>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="66" spans="17:29" x14ac:dyDescent="0.35">
       <c r="AA66" s="80"/>
       <c r="AB66" s="80"/>
       <c r="AC66" s="80"/>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="67" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q67" s="45"/>
       <c r="R67" s="45"/>
       <c r="S67" s="45"/>
@@ -9731,7 +9731,7 @@
       <c r="AB67" s="80"/>
       <c r="AC67" s="80"/>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="68" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q68" s="45"/>
       <c r="R68" s="45"/>
       <c r="S68" s="45"/>
@@ -9746,7 +9746,7 @@
       <c r="AB68" s="80"/>
       <c r="AC68" s="80"/>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="69" spans="17:29" x14ac:dyDescent="0.35">
       <c r="Q69" s="45"/>
       <c r="R69" s="45"/>
       <c r="S69" s="45"/>
@@ -9760,359 +9760,6 @@
       <c r="AA69" s="80"/>
       <c r="AB69" s="80"/>
       <c r="AC69" s="80"/>
-    </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q70" s="45"/>
-      <c r="R70" s="45"/>
-      <c r="S70" s="45"/>
-      <c r="T70" s="45"/>
-      <c r="U70" s="45"/>
-      <c r="V70" s="45"/>
-      <c r="W70" s="45"/>
-      <c r="X70" s="45"/>
-      <c r="Y70" s="45"/>
-      <c r="Z70" s="45"/>
-      <c r="AA70" s="80"/>
-      <c r="AB70" s="80"/>
-      <c r="AC70" s="80"/>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q71" s="45"/>
-      <c r="R71" s="45"/>
-      <c r="S71" s="45"/>
-      <c r="T71" s="45"/>
-      <c r="U71" s="45"/>
-      <c r="V71" s="45"/>
-      <c r="W71" s="45"/>
-      <c r="X71" s="45"/>
-      <c r="Y71" s="45"/>
-      <c r="Z71" s="45"/>
-      <c r="AA71" s="80"/>
-      <c r="AB71" s="80"/>
-      <c r="AC71" s="80"/>
-    </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q72" s="45"/>
-      <c r="R72" s="45"/>
-      <c r="S72" s="45"/>
-      <c r="T72" s="45"/>
-      <c r="U72" s="45"/>
-      <c r="V72" s="45"/>
-      <c r="W72" s="45"/>
-      <c r="X72" s="45"/>
-      <c r="Y72" s="45"/>
-      <c r="Z72" s="45"/>
-      <c r="AA72" s="78"/>
-      <c r="AB72" s="78"/>
-      <c r="AC72" s="78"/>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q73" s="45"/>
-      <c r="R73" s="45"/>
-      <c r="S73" s="45"/>
-      <c r="T73" s="45"/>
-      <c r="U73" s="45"/>
-      <c r="V73" s="45"/>
-      <c r="W73" s="45"/>
-      <c r="X73" s="45"/>
-      <c r="Y73" s="45"/>
-      <c r="Z73" s="45"/>
-      <c r="AA73" s="80"/>
-      <c r="AB73" s="80"/>
-      <c r="AC73" s="45"/>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A74" s="45"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45"/>
-      <c r="I74" s="45"/>
-      <c r="J74" s="45"/>
-      <c r="K74" s="45"/>
-      <c r="L74" s="45"/>
-      <c r="M74" s="45"/>
-      <c r="N74" s="45"/>
-      <c r="O74" s="45"/>
-      <c r="P74" s="45"/>
-      <c r="Q74" s="45"/>
-      <c r="R74" s="45"/>
-      <c r="S74" s="45"/>
-      <c r="T74" s="45"/>
-      <c r="U74" s="45"/>
-      <c r="V74" s="45"/>
-      <c r="W74" s="45"/>
-      <c r="X74" s="45"/>
-      <c r="Y74" s="45"/>
-      <c r="Z74" s="45"/>
-      <c r="AA74" s="80"/>
-      <c r="AB74" s="80"/>
-      <c r="AC74" s="80"/>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A75" s="45"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="45"/>
-      <c r="K75" s="45"/>
-      <c r="L75" s="45"/>
-      <c r="M75" s="45"/>
-      <c r="N75" s="45"/>
-      <c r="O75" s="45"/>
-      <c r="P75" s="45"/>
-      <c r="Q75" s="45"/>
-      <c r="R75" s="45"/>
-      <c r="S75" s="45"/>
-      <c r="T75" s="45"/>
-      <c r="U75" s="45"/>
-      <c r="V75" s="45"/>
-      <c r="W75" s="45"/>
-      <c r="X75" s="45"/>
-      <c r="Y75" s="45"/>
-      <c r="Z75" s="45"/>
-      <c r="AA75" s="78"/>
-      <c r="AB75" s="78"/>
-      <c r="AC75" s="78"/>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A76" s="45"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="45"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="45"/>
-      <c r="J76" s="45"/>
-      <c r="K76" s="45"/>
-      <c r="L76" s="45"/>
-      <c r="M76" s="45"/>
-      <c r="N76" s="45"/>
-      <c r="O76" s="45"/>
-      <c r="P76" s="45"/>
-      <c r="Q76" s="45"/>
-      <c r="R76" s="45"/>
-      <c r="S76" s="45"/>
-      <c r="T76" s="45"/>
-      <c r="U76" s="45"/>
-      <c r="V76" s="45"/>
-      <c r="W76" s="45"/>
-      <c r="X76" s="45"/>
-      <c r="Y76" s="45"/>
-      <c r="Z76" s="45"/>
-      <c r="AA76" s="78"/>
-      <c r="AB76" s="80"/>
-      <c r="AC76" s="80"/>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A77" s="45"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-      <c r="F77" s="45"/>
-      <c r="G77" s="45"/>
-      <c r="H77" s="45"/>
-      <c r="I77" s="45"/>
-      <c r="J77" s="45"/>
-      <c r="K77" s="45"/>
-      <c r="L77" s="45"/>
-      <c r="M77" s="45"/>
-      <c r="N77" s="45"/>
-      <c r="O77" s="45"/>
-      <c r="P77" s="45"/>
-      <c r="Q77" s="45"/>
-      <c r="R77" s="45"/>
-      <c r="S77" s="45"/>
-      <c r="T77" s="45"/>
-      <c r="U77" s="45"/>
-      <c r="V77" s="45"/>
-      <c r="W77" s="45"/>
-      <c r="X77" s="45"/>
-      <c r="Y77" s="45"/>
-      <c r="Z77" s="45"/>
-      <c r="AA77" s="78"/>
-      <c r="AB77" s="80"/>
-      <c r="AC77" s="80"/>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A78" s="45"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45"/>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45"/>
-      <c r="L78" s="45"/>
-      <c r="M78" s="45"/>
-      <c r="N78" s="45"/>
-      <c r="O78" s="45"/>
-      <c r="P78" s="45"/>
-      <c r="Q78" s="45"/>
-      <c r="R78" s="45"/>
-      <c r="S78" s="45"/>
-      <c r="T78" s="45"/>
-      <c r="U78" s="45"/>
-      <c r="V78" s="45"/>
-      <c r="W78" s="45"/>
-      <c r="X78" s="45"/>
-      <c r="Y78" s="45"/>
-      <c r="Z78" s="45"/>
-      <c r="AA78" s="78"/>
-      <c r="AB78" s="80"/>
-      <c r="AC78" s="80"/>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A79" s="45"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="45"/>
-      <c r="F79" s="45"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
-      <c r="I79" s="45"/>
-      <c r="J79" s="45"/>
-      <c r="K79" s="45"/>
-      <c r="L79" s="45"/>
-      <c r="M79" s="45"/>
-      <c r="N79" s="45"/>
-      <c r="O79" s="45"/>
-      <c r="P79" s="45"/>
-      <c r="Q79" s="45"/>
-      <c r="R79" s="45"/>
-      <c r="S79" s="45"/>
-      <c r="T79" s="45"/>
-      <c r="U79" s="45"/>
-      <c r="V79" s="45"/>
-      <c r="W79" s="45"/>
-      <c r="X79" s="45"/>
-      <c r="Y79" s="45"/>
-      <c r="Z79" s="45"/>
-      <c r="AA79" s="78"/>
-      <c r="AB79" s="80"/>
-      <c r="AC79" s="80"/>
-    </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A80" s="45"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45"/>
-      <c r="I80" s="45"/>
-      <c r="J80" s="45"/>
-      <c r="K80" s="45"/>
-      <c r="L80" s="45"/>
-      <c r="M80" s="45"/>
-      <c r="N80" s="45"/>
-      <c r="O80" s="45"/>
-      <c r="P80" s="45"/>
-      <c r="Q80" s="45"/>
-      <c r="R80" s="45"/>
-      <c r="S80" s="45"/>
-      <c r="T80" s="45"/>
-      <c r="U80" s="45"/>
-      <c r="V80" s="45"/>
-      <c r="W80" s="45"/>
-      <c r="X80" s="45"/>
-      <c r="Y80" s="45"/>
-      <c r="Z80" s="45"/>
-      <c r="AA80" s="78"/>
-      <c r="AB80" s="80"/>
-      <c r="AC80" s="80"/>
-    </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A81" s="45"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
-      <c r="D81" s="45"/>
-      <c r="E81" s="45"/>
-      <c r="F81" s="45"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45"/>
-      <c r="I81" s="45"/>
-      <c r="J81" s="45"/>
-      <c r="K81" s="45"/>
-      <c r="L81" s="45"/>
-      <c r="M81" s="45"/>
-      <c r="N81" s="45"/>
-      <c r="O81" s="45"/>
-      <c r="P81" s="45"/>
-      <c r="Q81" s="45"/>
-      <c r="R81" s="45"/>
-      <c r="S81" s="45"/>
-      <c r="T81" s="45"/>
-      <c r="U81" s="45"/>
-      <c r="V81" s="45"/>
-      <c r="W81" s="45"/>
-      <c r="X81" s="45"/>
-      <c r="Y81" s="45"/>
-      <c r="Z81" s="45"/>
-      <c r="AA81" s="45"/>
-      <c r="AB81" s="45"/>
-      <c r="AC81" s="45"/>
-    </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q82" s="45"/>
-      <c r="R82" s="45"/>
-      <c r="S82" s="45"/>
-      <c r="T82" s="45"/>
-      <c r="U82" s="45"/>
-      <c r="V82" s="45"/>
-      <c r="W82" s="45"/>
-      <c r="X82" s="45"/>
-      <c r="Y82" s="45"/>
-      <c r="Z82" s="45"/>
-      <c r="AA82" s="45"/>
-      <c r="AB82" s="45"/>
-      <c r="AC82" s="45"/>
-    </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q83" s="45"/>
-      <c r="R83" s="45"/>
-      <c r="S83" s="45"/>
-      <c r="T83" s="45"/>
-      <c r="U83" s="45"/>
-      <c r="V83" s="45"/>
-      <c r="W83" s="45"/>
-      <c r="X83" s="45"/>
-      <c r="Y83" s="45"/>
-      <c r="Z83" s="45"/>
-      <c r="AA83" s="45"/>
-      <c r="AB83" s="45"/>
-      <c r="AC83" s="45"/>
-    </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="Q84" s="45"/>
-      <c r="R84" s="45"/>
-      <c r="S84" s="45"/>
-      <c r="T84" s="45"/>
-      <c r="U84" s="45"/>
-      <c r="V84" s="45"/>
-      <c r="W84" s="45"/>
-      <c r="X84" s="45"/>
-      <c r="Y84" s="45"/>
-      <c r="Z84" s="45"/>
-      <c r="AA84" s="45"/>
-      <c r="AB84" s="45"/>
-      <c r="AC84" s="45"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC65"/>
@@ -10654,7 +10301,7 @@
         <v>628</v>
       </c>
       <c r="F2" s="52" t="str">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC88,27,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC69,27,0)</f>
         <v>OTH</v>
       </c>
     </row>
@@ -10670,7 +10317,7 @@
         <v>601</v>
       </c>
       <c r="F3" s="52">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC89,28,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:AC69,28,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10686,7 +10333,7 @@
         <v>627</v>
       </c>
       <c r="F4" s="52">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A2:AC90,29,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A2:AC69,29,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -10738,7 +10385,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="48" t="str">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z70,24,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,24,0)</f>
         <v>VISHWAKARMA NAGAR RENUKOOT</v>
       </c>
       <c r="F8" s="44"/>
@@ -10763,7 +10410,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="82">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z72,25,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,25,0)</f>
         <v>9519725292</v>
       </c>
       <c r="P9">
@@ -10775,7 +10422,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="48" t="str">
-        <f>LOWER(VLOOKUP($C$1,'Sheet1 (5)'!A1:Z74,26,0))</f>
+        <f>LOWER(VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,26,0))</f>
         <v>awanitk94@gmail.com</v>
       </c>
       <c r="F10" s="44" t="s">
@@ -10814,7 +10461,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="48">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z76,5,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,5,0)</f>
         <v>21573201849</v>
       </c>
       <c r="F12" s="44"/>
@@ -10840,7 +10487,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="52">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z78,6,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,6,0)</f>
         <v>940879560324</v>
       </c>
     </row>
@@ -10853,7 +10500,7 @@
         <v>591</v>
       </c>
       <c r="C15" s="52" t="str">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z80,20,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,20,0)</f>
         <v>OBC</v>
       </c>
       <c r="F15" s="44" t="s">
@@ -10872,7 +10519,7 @@
         <v>592</v>
       </c>
       <c r="C16" s="52" t="str">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z82,19,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,19,0)</f>
         <v>RONIYAR</v>
       </c>
       <c r="F16" s="44" t="s">
@@ -10891,7 +10538,7 @@
         <v>593</v>
       </c>
       <c r="C17" s="52" t="str">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z84,17,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,17,0)</f>
         <v>M</v>
       </c>
       <c r="F17" s="44"/>
@@ -10913,7 +10560,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="52" t="str">
-        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z86,22,0)</f>
+        <f>VLOOKUP($C$1,'Sheet1 (5)'!A1:Z69,22,0)</f>
         <v>H</v>
       </c>
     </row>
